--- a/data/CROSS/EXCLE/SIVEF_1_20261005.xlsx
+++ b/data/CROSS/EXCLE/SIVEF_1_20261005.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'30日跟踪'!$A$8</f>
+              <f>'30日跟踪'!$A$8:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'30日跟踪'!$D$8</f>
+              <f>'30日跟踪'!$D$8:$D$9</f>
             </numRef>
           </val>
         </ser>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>3.430000066757202</v>
+        <v>3.440000057220459</v>
       </c>
     </row>
     <row r="6">
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
     </row>
     <row r="7">
@@ -696,10 +696,10 @@
         <v>46300</v>
       </c>
       <c r="B8" s="4" t="n">
-        <v>3.430000066757202</v>
+        <v>3.440000057220459</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>5.538463592529297</v>
+        <v>5.846155606783343</v>
       </c>
       <c r="D8" s="6">
         <f>B8/$B$8-1</f>
@@ -708,6 +708,26 @@
       <c r="E8" t="inlineStr">
         <is>
           <t>第1/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>3.490000009536743</v>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>1.453486961761397</v>
+      </c>
+      <c r="D9" s="6">
+        <f>B9/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>第2/30个交易日</t>
         </is>
       </c>
     </row>

--- a/data/CROSS/EXCLE/SIVEF_1_20261005.xlsx
+++ b/data/CROSS/EXCLE/SIVEF_1_20261005.xlsx
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
     </row>
     <row r="7">
@@ -716,10 +716,10 @@
         <v>46301</v>
       </c>
       <c r="B9" s="4" t="n">
-        <v>3.490000009536743</v>
+        <v>3.5</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>1.453486961761397</v>
+        <v>1.744184354113676</v>
       </c>
       <c r="D9" s="6">
         <f>B9/$B$8-1</f>

--- a/data/CROSS/EXCLE/SIVEF_1_20261005.xlsx
+++ b/data/CROSS/EXCLE/SIVEF_1_20261005.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'30日跟踪'!$A$8:$A$9</f>
+              <f>'30日跟踪'!$A$8:$A$11</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'30日跟踪'!$D$8:$D$9</f>
+              <f>'30日跟踪'!$D$8:$D$11</f>
             </numRef>
           </val>
         </ser>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
     </row>
     <row r="7">
@@ -728,6 +728,46 @@
       <c r="E9" t="inlineStr">
         <is>
           <t>第2/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>3.480000019073486</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>-0.5714280264718208</v>
+      </c>
+      <c r="D10" s="6">
+        <f>B10/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>第3/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>2.990000009536743</v>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>-14.08045996698588</v>
+      </c>
+      <c r="D11" s="6">
+        <f>B11/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>第4/30个交易日</t>
         </is>
       </c>
     </row>

--- a/data/CROSS/EXCLE/SIVEF_1_20261005.xlsx
+++ b/data/CROSS/EXCLE/SIVEF_1_20261005.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'30日跟踪'!$A$8:$A$11</f>
+              <f>'30日跟踪'!$A$8:$A$12</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'30日跟踪'!$D$8:$D$11</f>
+              <f>'30日跟踪'!$D$8:$D$12</f>
             </numRef>
           </val>
         </ser>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="7">
@@ -768,6 +768,26 @@
       <c r="E11" t="inlineStr">
         <is>
           <t>第4/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B12" s="4" t="n">
+        <v>2.960000038146973</v>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>-1.003343521541278</v>
+      </c>
+      <c r="D12" s="6">
+        <f>B12/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>第5/30个交易日</t>
         </is>
       </c>
     </row>

--- a/data/CROSS/EXCLE/SIVEF_1_20261005.xlsx
+++ b/data/CROSS/EXCLE/SIVEF_1_20261005.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'30日跟踪'!$A$8:$A$12</f>
+              <f>'30日跟踪'!$A$8:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'30日跟踪'!$D$8:$D$12</f>
+              <f>'30日跟踪'!$D$8:$D$13</f>
             </numRef>
           </val>
         </ser>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46304</v>
+        <v>46307</v>
       </c>
     </row>
     <row r="7">
@@ -788,6 +788,26 @@
       <c r="E12" t="inlineStr">
         <is>
           <t>第5/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B13" s="4" t="n">
+        <v>2.740000009536743</v>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>-7.432433303208819</v>
+      </c>
+      <c r="D13" s="6">
+        <f>B13/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>第6/30个交易日</t>
         </is>
       </c>
     </row>

--- a/data/CROSS/EXCLE/SIVEF_1_20261005.xlsx
+++ b/data/CROSS/EXCLE/SIVEF_1_20261005.xlsx
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="7">

--- a/data/CROSS/EXCLE/SIVEF_1_20261005.xlsx
+++ b/data/CROSS/EXCLE/SIVEF_1_20261005.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'30日跟踪'!$A$8:$A$13</f>
+              <f>'30日跟踪'!$A$8:$A$15</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'30日跟踪'!$D$8:$D$13</f>
+              <f>'30日跟踪'!$D$8:$D$15</f>
             </numRef>
           </val>
         </ser>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="7">
@@ -808,6 +808,46 @@
       <c r="E13" t="inlineStr">
         <is>
           <t>第6/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B14" s="4" t="n">
+        <v>2.599999904632568</v>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>-5.109492861930498</v>
+      </c>
+      <c r="D14" s="6">
+        <f>B14/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>第7/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B15" s="4" t="n">
+        <v>2.569999933242798</v>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>-1.153845095775496</v>
+      </c>
+      <c r="D15" s="6">
+        <f>B15/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>第8/30个交易日</t>
         </is>
       </c>
     </row>

--- a/data/CROSS/EXCLE/SIVEF_1_20261005.xlsx
+++ b/data/CROSS/EXCLE/SIVEF_1_20261005.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'30日跟踪'!$A$8:$A$15</f>
+              <f>'30日跟踪'!$A$8:$A$16</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'30日跟踪'!$D$8:$D$15</f>
+              <f>'30日跟踪'!$D$8:$D$16</f>
             </numRef>
           </val>
         </ser>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="7">
@@ -836,10 +836,10 @@
         <v>46309</v>
       </c>
       <c r="B15" s="4" t="n">
-        <v>2.569999933242798</v>
+        <v>2.539999961853027</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-1.153845095775496</v>
+        <v>-2.307690191550993</v>
       </c>
       <c r="D15" s="6">
         <f>B15/$B$8-1</f>
@@ -848,6 +848,26 @@
       <c r="E15" t="inlineStr">
         <is>
           <t>第8/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B16" s="4" t="n">
+        <v>2.549999952316284</v>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>0.3937004178520276</v>
+      </c>
+      <c r="D16" s="6">
+        <f>B16/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>第9/30个交易日</t>
         </is>
       </c>
     </row>

--- a/data/CROSS/EXCLE/SIVEF_1_20261005.xlsx
+++ b/data/CROSS/EXCLE/SIVEF_1_20261005.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'30日跟踪'!$A$8:$A$16</f>
+              <f>'30日跟踪'!$A$8:$A$17</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'30日跟踪'!$D$8:$D$16</f>
+              <f>'30日跟踪'!$D$8:$D$17</f>
             </numRef>
           </val>
         </ser>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="7">
@@ -856,10 +856,10 @@
         <v>46310</v>
       </c>
       <c r="B16" s="4" t="n">
-        <v>2.549999952316284</v>
+        <v>2.54010009765625</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.3937004178520276</v>
+        <v>0.003942354516794921</v>
       </c>
       <c r="D16" s="6">
         <f>B16/$B$8-1</f>
@@ -868,6 +868,26 @@
       <c r="E16" t="inlineStr">
         <is>
           <t>第9/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B17" s="4" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>-11.42081360982291</v>
+      </c>
+      <c r="D17" s="6">
+        <f>B17/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>第10/30个交易日</t>
         </is>
       </c>
     </row>

--- a/data/CROSS/EXCLE/SIVEF_1_20261005.xlsx
+++ b/data/CROSS/EXCLE/SIVEF_1_20261005.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'30日跟踪'!$A$8:$A$17</f>
+              <f>'30日跟踪'!$A$8:$A$18</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'30日跟踪'!$D$8:$D$17</f>
+              <f>'30日跟踪'!$D$8:$D$18</f>
             </numRef>
           </val>
         </ser>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46311</v>
+        <v>46314</v>
       </c>
     </row>
     <row r="7">
@@ -888,6 +888,26 @@
       <c r="E17" t="inlineStr">
         <is>
           <t>第10/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B18" s="4" t="n">
+        <v>2.259999990463257</v>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>0.4444440205891853</v>
+      </c>
+      <c r="D18" s="6">
+        <f>B18/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>第11/30个交易日</t>
         </is>
       </c>
     </row>

--- a/data/CROSS/EXCLE/SIVEF_1_20261005.xlsx
+++ b/data/CROSS/EXCLE/SIVEF_1_20261005.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'30日跟踪'!$A$8:$A$18</f>
+              <f>'30日跟踪'!$A$8:$A$19</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'30日跟踪'!$D$8:$D$18</f>
+              <f>'30日跟踪'!$D$8:$D$19</f>
             </numRef>
           </val>
         </ser>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
     </row>
     <row r="7">
@@ -908,6 +908,26 @@
       <c r="E18" t="inlineStr">
         <is>
           <t>第11/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B19" s="4" t="n">
+        <v>2.390000104904175</v>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>5.752217477411148</v>
+      </c>
+      <c r="D19" s="6">
+        <f>B19/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>第12/30个交易日</t>
         </is>
       </c>
     </row>

--- a/data/CROSS/EXCLE/SIVEF_1_20261005.xlsx
+++ b/data/CROSS/EXCLE/SIVEF_1_20261005.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'30日跟踪'!$A$8:$A$19</f>
+              <f>'30日跟踪'!$A$8:$A$20</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'30日跟踪'!$D$8:$D$19</f>
+              <f>'30日跟踪'!$D$8:$D$20</f>
             </numRef>
           </val>
         </ser>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
     </row>
     <row r="7">
@@ -928,6 +928,26 @@
       <c r="E19" t="inlineStr">
         <is>
           <t>第12/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B20" s="4" t="n">
+        <v>2.450000047683716</v>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>2.51045774669314</v>
+      </c>
+      <c r="D20" s="6">
+        <f>B20/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>第13/30个交易日</t>
         </is>
       </c>
     </row>

--- a/data/CROSS/EXCLE/SIVEF_1_20261005.xlsx
+++ b/data/CROSS/EXCLE/SIVEF_1_20261005.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'30日跟踪'!$A$8:$A$20</f>
+              <f>'30日跟踪'!$A$8:$A$21</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'30日跟踪'!$D$8:$D$20</f>
+              <f>'30日跟踪'!$D$8:$D$21</f>
             </numRef>
           </val>
         </ser>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
     </row>
     <row r="7">
@@ -936,10 +936,10 @@
         <v>46316</v>
       </c>
       <c r="B20" s="4" t="n">
-        <v>2.450000047683716</v>
+        <v>2.454999923706055</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>2.51045774669314</v>
+        <v>2.719657571081413</v>
       </c>
       <c r="D20" s="6">
         <f>B20/$B$8-1</f>
@@ -948,6 +948,26 @@
       <c r="E20" t="inlineStr">
         <is>
           <t>第13/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B21" s="4" t="n">
+        <v>2.079999923706055</v>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>-15.2749495582021</v>
+      </c>
+      <c r="D21" s="6">
+        <f>B21/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>第14/30个交易日</t>
         </is>
       </c>
     </row>

--- a/data/CROSS/EXCLE/SIVEF_1_20261005.xlsx
+++ b/data/CROSS/EXCLE/SIVEF_1_20261005.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'30日跟踪'!$A$8:$A$21</f>
+              <f>'30日跟踪'!$A$8:$A$22</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'30日跟踪'!$D$8:$D$21</f>
+              <f>'30日跟踪'!$D$8:$D$22</f>
             </numRef>
           </val>
         </ser>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
     </row>
     <row r="7">
@@ -956,10 +956,10 @@
         <v>46317</v>
       </c>
       <c r="B21" s="4" t="n">
-        <v>2.079999923706055</v>
+        <v>2.069999933242798</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-15.2749495582021</v>
+        <v>-15.68228115795877</v>
       </c>
       <c r="D21" s="6">
         <f>B21/$B$8-1</f>
@@ -968,6 +968,26 @@
       <c r="E21" t="inlineStr">
         <is>
           <t>第14/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B22" s="4" t="n">
+        <v>2.019999980926514</v>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>-2.415456711535047</v>
+      </c>
+      <c r="D22" s="6">
+        <f>B22/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>第15/30个交易日</t>
         </is>
       </c>
     </row>

--- a/data/CROSS/EXCLE/SIVEF_1_20261005.xlsx
+++ b/data/CROSS/EXCLE/SIVEF_1_20261005.xlsx
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46318</v>
+        <v>46321</v>
       </c>
     </row>
     <row r="7">

--- a/data/CROSS/EXCLE/SIVEF_1_20261005.xlsx
+++ b/data/CROSS/EXCLE/SIVEF_1_20261005.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'30日跟踪'!$A$8:$A$22</f>
+              <f>'30日跟踪'!$A$8:$A$23</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'30日跟踪'!$D$8:$D$22</f>
+              <f>'30日跟踪'!$D$8:$D$23</f>
             </numRef>
           </val>
         </ser>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
     </row>
     <row r="7">
@@ -988,6 +988,26 @@
       <c r="E22" t="inlineStr">
         <is>
           <t>第15/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B23" s="4" t="n">
+        <v>2.109999895095825</v>
+      </c>
+      <c r="C23" s="4" t="n">
+        <v>4.455441337580179</v>
+      </c>
+      <c r="D23" s="6">
+        <f>B23/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>第16/30个交易日</t>
         </is>
       </c>
     </row>

--- a/data/CROSS/EXCLE/SIVEF_1_20261005.xlsx
+++ b/data/CROSS/EXCLE/SIVEF_1_20261005.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'30日跟踪'!$A$8:$A$23</f>
+              <f>'30日跟踪'!$A$8:$A$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'30日跟踪'!$D$8:$D$23</f>
+              <f>'30日跟踪'!$D$8:$D$25</f>
             </numRef>
           </val>
         </ser>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
     </row>
     <row r="7">
@@ -1008,6 +1008,46 @@
       <c r="E23" t="inlineStr">
         <is>
           <t>第16/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B24" s="4" t="n">
+        <v>2.309999942779541</v>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>9.478675716930907</v>
+      </c>
+      <c r="D24" s="6">
+        <f>B24/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>第17/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B25" s="4" t="n">
+        <v>2.319999933242798</v>
+      </c>
+      <c r="C25" s="4" t="n">
+        <v>0.432900030777672</v>
+      </c>
+      <c r="D25" s="6">
+        <f>B25/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>第18/30个交易日</t>
         </is>
       </c>
     </row>

--- a/data/CROSS/EXCLE/SIVEF_1_20261005.xlsx
+++ b/data/CROSS/EXCLE/SIVEF_1_20261005.xlsx
@@ -196,12 +196,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'30日跟踪'!$A$8:$A$25</f>
+              <f>'30日跟踪'!$A$8:$A$26</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'30日跟踪'!$D$8:$D$25</f>
+              <f>'30日跟踪'!$D$8:$D$26</f>
             </numRef>
           </val>
         </ser>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -661,7 +661,7 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
     </row>
     <row r="7">
@@ -1048,6 +1048,26 @@
       <c r="E25" t="inlineStr">
         <is>
           <t>第18/30个交易日</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B26" s="4" t="n">
+        <v>2.319999933242798</v>
+      </c>
+      <c r="C26" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="6">
+        <f>B26/$B$8-1</f>
+        <v/>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>第19/30个交易日</t>
         </is>
       </c>
     </row>
